--- a/data/nzd0157/nzd0157.xlsx
+++ b/data/nzd0157/nzd0157.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q351"/>
+  <dimension ref="A1:Q352"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20444,6 +20444,63 @@
         </is>
       </c>
     </row>
+    <row r="352">
+      <c r="A352" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B352" t="n">
+        <v>389.35</v>
+      </c>
+      <c r="C352" t="n">
+        <v>373.73</v>
+      </c>
+      <c r="D352" t="n">
+        <v>376.59</v>
+      </c>
+      <c r="E352" t="n">
+        <v>372.87</v>
+      </c>
+      <c r="F352" t="n">
+        <v>368.25</v>
+      </c>
+      <c r="G352" t="n">
+        <v>369.5</v>
+      </c>
+      <c r="H352" t="n">
+        <v>370.47</v>
+      </c>
+      <c r="I352" t="n">
+        <v>371.55</v>
+      </c>
+      <c r="J352" t="n">
+        <v>370.07</v>
+      </c>
+      <c r="K352" t="n">
+        <v>368.85</v>
+      </c>
+      <c r="L352" t="n">
+        <v>363.76</v>
+      </c>
+      <c r="M352" t="n">
+        <v>366.09</v>
+      </c>
+      <c r="N352" t="n">
+        <v>374.55</v>
+      </c>
+      <c r="O352" t="n">
+        <v>383.38</v>
+      </c>
+      <c r="P352" t="n">
+        <v>352.96</v>
+      </c>
+      <c r="Q352" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -20455,7 +20512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B367"/>
+  <dimension ref="A1:B368"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24128,6 +24185,16 @@
       </c>
       <c r="B367" t="n">
         <v>-0.43</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B368" t="n">
+        <v>0.55</v>
       </c>
     </row>
   </sheetData>
@@ -24296,28 +24363,28 @@
         <v>0.0555</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2667174769854604</v>
+        <v>0.2677937261564768</v>
       </c>
       <c r="J2" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K2" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2458574017241557</v>
+        <v>0.2483491768884566</v>
       </c>
       <c r="M2" t="n">
-        <v>2.59281129370842</v>
+        <v>2.590899837138472</v>
       </c>
       <c r="N2" t="n">
-        <v>11.79557230548347</v>
+        <v>11.77207107936029</v>
       </c>
       <c r="O2" t="n">
-        <v>3.434468271142343</v>
+        <v>3.431045187601045</v>
       </c>
       <c r="P2" t="n">
-        <v>380.3933944925836</v>
+        <v>380.3819408227613</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -24374,28 +24441,28 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3730130870117748</v>
+        <v>0.371762649090603</v>
       </c>
       <c r="J3" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K3" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2763636868552138</v>
+        <v>0.2761213909284975</v>
       </c>
       <c r="M3" t="n">
-        <v>3.552497358047509</v>
+        <v>3.548730892283378</v>
       </c>
       <c r="N3" t="n">
-        <v>19.69397561923775</v>
+        <v>19.65150725290297</v>
       </c>
       <c r="O3" t="n">
-        <v>4.437789496949777</v>
+        <v>4.433002058752395</v>
       </c>
       <c r="P3" t="n">
-        <v>366.0504081416726</v>
+        <v>366.063715564775</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -24452,28 +24519,28 @@
         <v>0.1281</v>
       </c>
       <c r="I4" t="n">
-        <v>0.329450104280983</v>
+        <v>0.3298842997096056</v>
       </c>
       <c r="J4" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K4" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2303849263194336</v>
+        <v>0.2319397114895836</v>
       </c>
       <c r="M4" t="n">
-        <v>3.356304747058728</v>
+        <v>3.348763966156936</v>
       </c>
       <c r="N4" t="n">
-        <v>19.59948620345383</v>
+        <v>19.54529179163935</v>
       </c>
       <c r="O4" t="n">
-        <v>4.427130696450448</v>
+        <v>4.421005744357198</v>
       </c>
       <c r="P4" t="n">
-        <v>367.1027844859715</v>
+        <v>367.0981636869859</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -24530,28 +24597,28 @@
         <v>0.09959999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2248217570584914</v>
+        <v>0.2244353640268314</v>
       </c>
       <c r="J5" t="n">
+        <v>351</v>
+      </c>
+      <c r="K5" t="n">
         <v>350</v>
       </c>
-      <c r="K5" t="n">
-        <v>349</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.1385967201930588</v>
+        <v>0.1389206746499988</v>
       </c>
       <c r="M5" t="n">
-        <v>3.139406569300172</v>
+        <v>3.132356740338393</v>
       </c>
       <c r="N5" t="n">
-        <v>16.80993785963319</v>
+        <v>16.76319262235232</v>
       </c>
       <c r="O5" t="n">
-        <v>4.099992421899483</v>
+        <v>4.094287804045084</v>
       </c>
       <c r="P5" t="n">
-        <v>367.5898143033082</v>
+        <v>367.5939552241982</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -24608,28 +24675,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1395498368916404</v>
+        <v>0.1400846446920316</v>
       </c>
       <c r="J6" t="n">
+        <v>351</v>
+      </c>
+      <c r="K6" t="n">
         <v>350</v>
       </c>
-      <c r="K6" t="n">
-        <v>349</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.06702560881506192</v>
+        <v>0.06788790606275696</v>
       </c>
       <c r="M6" t="n">
-        <v>2.913629092999888</v>
+        <v>2.907458132561673</v>
       </c>
       <c r="N6" t="n">
-        <v>14.50519216932569</v>
+        <v>14.46620695941371</v>
       </c>
       <c r="O6" t="n">
-        <v>3.808568257144105</v>
+        <v>3.803446720990542</v>
       </c>
       <c r="P6" t="n">
-        <v>363.6268660948121</v>
+        <v>363.6211346332915</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -24686,28 +24753,28 @@
         <v>0.1229</v>
       </c>
       <c r="I7" t="n">
-        <v>0.214213956633857</v>
+        <v>0.2155097455205759</v>
       </c>
       <c r="J7" t="n">
+        <v>351</v>
+      </c>
+      <c r="K7" t="n">
         <v>350</v>
       </c>
-      <c r="K7" t="n">
-        <v>349</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.1592360294887575</v>
+        <v>0.1615487118275185</v>
       </c>
       <c r="M7" t="n">
-        <v>2.868168664773836</v>
+        <v>2.865082833381128</v>
       </c>
       <c r="N7" t="n">
-        <v>12.96474989235303</v>
+        <v>12.94213852276548</v>
       </c>
       <c r="O7" t="n">
-        <v>3.600659646835983</v>
+        <v>3.59751838393711</v>
       </c>
       <c r="P7" t="n">
-        <v>361.5673805446569</v>
+        <v>361.5534937536685</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -24764,28 +24831,28 @@
         <v>0.074</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2168141103022296</v>
+        <v>0.2196409433518784</v>
       </c>
       <c r="J8" t="n">
+        <v>351</v>
+      </c>
+      <c r="K8" t="n">
         <v>350</v>
       </c>
-      <c r="K8" t="n">
-        <v>349</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.1292321601238787</v>
+        <v>0.1324250401337432</v>
       </c>
       <c r="M8" t="n">
-        <v>3.221194515898365</v>
+        <v>3.224611483303494</v>
       </c>
       <c r="N8" t="n">
-        <v>16.94894722788816</v>
+        <v>16.96920026105835</v>
       </c>
       <c r="O8" t="n">
-        <v>4.116909912530048</v>
+        <v>4.119368915387204</v>
       </c>
       <c r="P8" t="n">
-        <v>359.8010180874749</v>
+        <v>359.7707233071122</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -24842,28 +24909,28 @@
         <v>0.09089999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>0.213594426609275</v>
+        <v>0.2160852249067947</v>
       </c>
       <c r="J9" t="n">
+        <v>351</v>
+      </c>
+      <c r="K9" t="n">
         <v>350</v>
       </c>
-      <c r="K9" t="n">
-        <v>349</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.1359333836151521</v>
+        <v>0.139013290908317</v>
       </c>
       <c r="M9" t="n">
-        <v>3.129448685987739</v>
+        <v>3.133043093490416</v>
       </c>
       <c r="N9" t="n">
-        <v>15.51803747516438</v>
+        <v>15.52702121625848</v>
       </c>
       <c r="O9" t="n">
-        <v>3.939294032585583</v>
+        <v>3.940434140581274</v>
       </c>
       <c r="P9" t="n">
-        <v>361.5522438516788</v>
+        <v>361.5255503094618</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -24920,28 +24987,28 @@
         <v>0.0915</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1597220776666913</v>
+        <v>0.1587342112613215</v>
       </c>
       <c r="J10" t="n">
+        <v>351</v>
+      </c>
+      <c r="K10" t="n">
         <v>350</v>
       </c>
-      <c r="K10" t="n">
-        <v>349</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.08413579015853367</v>
+        <v>0.08361738486286252</v>
       </c>
       <c r="M10" t="n">
-        <v>3.025271780163726</v>
+        <v>3.020969901715064</v>
       </c>
       <c r="N10" t="n">
-        <v>14.85990649795356</v>
+        <v>14.82583683240268</v>
       </c>
       <c r="O10" t="n">
-        <v>3.854854925668872</v>
+        <v>3.850433330471089</v>
       </c>
       <c r="P10" t="n">
-        <v>367.5576215075162</v>
+        <v>367.568208335692</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -24998,28 +25065,28 @@
         <v>0.0954</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1547784637850843</v>
+        <v>0.1551973217874049</v>
       </c>
       <c r="J11" t="n">
+        <v>351</v>
+      </c>
+      <c r="K11" t="n">
         <v>350</v>
       </c>
-      <c r="K11" t="n">
-        <v>349</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.07515312525600326</v>
+        <v>0.07595893534622411</v>
       </c>
       <c r="M11" t="n">
-        <v>3.181952989251405</v>
+        <v>3.175033326356429</v>
       </c>
       <c r="N11" t="n">
-        <v>15.77537589249173</v>
+        <v>15.73181122808873</v>
       </c>
       <c r="O11" t="n">
-        <v>3.971822741826696</v>
+        <v>3.966334734750551</v>
       </c>
       <c r="P11" t="n">
-        <v>364.0196216762595</v>
+        <v>364.0151328327514</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -25076,28 +25143,28 @@
         <v>0.0953</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1827609557708264</v>
+        <v>0.1810545770265446</v>
       </c>
       <c r="J12" t="n">
+        <v>351</v>
+      </c>
+      <c r="K12" t="n">
         <v>350</v>
       </c>
-      <c r="K12" t="n">
-        <v>349</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.100251265144491</v>
+        <v>0.0989868743735024</v>
       </c>
       <c r="M12" t="n">
-        <v>3.141351981491778</v>
+        <v>3.139597811406075</v>
       </c>
       <c r="N12" t="n">
-        <v>16.04109787210207</v>
+        <v>16.02029104123652</v>
       </c>
       <c r="O12" t="n">
-        <v>4.005133939346107</v>
+        <v>4.002535576511034</v>
       </c>
       <c r="P12" t="n">
-        <v>361.88939103501</v>
+        <v>361.9076780609382</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -25154,28 +25221,28 @@
         <v>0.0854</v>
       </c>
       <c r="I13" t="n">
-        <v>0.27295064233879</v>
+        <v>0.2700302582411133</v>
       </c>
       <c r="J13" t="n">
+        <v>351</v>
+      </c>
+      <c r="K13" t="n">
         <v>350</v>
       </c>
-      <c r="K13" t="n">
-        <v>349</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.165789538358361</v>
+        <v>0.1631860621766186</v>
       </c>
       <c r="M13" t="n">
-        <v>3.372165880451435</v>
+        <v>3.377792385728061</v>
       </c>
       <c r="N13" t="n">
-        <v>20.05961603306949</v>
+        <v>20.075602349441</v>
       </c>
       <c r="O13" t="n">
-        <v>4.478796270547421</v>
+        <v>4.480580581737259</v>
       </c>
       <c r="P13" t="n">
-        <v>363.9522621106252</v>
+        <v>363.9835594646818</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -25232,28 +25299,28 @@
         <v>0.0863</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3103723116195351</v>
+        <v>0.3101444035328778</v>
       </c>
       <c r="J14" t="n">
+        <v>351</v>
+      </c>
+      <c r="K14" t="n">
         <v>350</v>
       </c>
-      <c r="K14" t="n">
-        <v>349</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.160127903784792</v>
+        <v>0.1607666603942077</v>
       </c>
       <c r="M14" t="n">
-        <v>4.02119474413051</v>
+        <v>4.010772829208173</v>
       </c>
       <c r="N14" t="n">
-        <v>27.03634256662844</v>
+        <v>26.95954229041427</v>
       </c>
       <c r="O14" t="n">
-        <v>5.199648311821525</v>
+        <v>5.19225791832554</v>
       </c>
       <c r="P14" t="n">
-        <v>366.7242681546584</v>
+        <v>366.7267106142261</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -25310,28 +25377,28 @@
         <v>0.0477</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5432368461853747</v>
+        <v>0.5426803137777474</v>
       </c>
       <c r="J15" t="n">
+        <v>351</v>
+      </c>
+      <c r="K15" t="n">
         <v>350</v>
       </c>
-      <c r="K15" t="n">
-        <v>349</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.1967258344978013</v>
+        <v>0.1973802833159548</v>
       </c>
       <c r="M15" t="n">
-        <v>5.829621674611611</v>
+        <v>5.815554417427907</v>
       </c>
       <c r="N15" t="n">
-        <v>64.47876440910076</v>
+        <v>64.29720133090379</v>
       </c>
       <c r="O15" t="n">
-        <v>8.029867023126894</v>
+        <v>8.018553568499982</v>
       </c>
       <c r="P15" t="n">
-        <v>369.9664564207889</v>
+        <v>369.9724207019325</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -25388,28 +25455,28 @@
         <v>0.0274</v>
       </c>
       <c r="I16" t="n">
-        <v>0.004422597890222277</v>
+        <v>-0.00376220284696303</v>
       </c>
       <c r="J16" t="n">
+        <v>351</v>
+      </c>
+      <c r="K16" t="n">
         <v>350</v>
       </c>
-      <c r="K16" t="n">
-        <v>349</v>
-      </c>
       <c r="L16" t="n">
-        <v>1.177949516273369e-05</v>
+        <v>8.522147533107649e-06</v>
       </c>
       <c r="M16" t="n">
-        <v>6.729000844630306</v>
+        <v>6.741444108528491</v>
       </c>
       <c r="N16" t="n">
-        <v>88.85031659045792</v>
+        <v>89.17221300689293</v>
       </c>
       <c r="O16" t="n">
-        <v>9.426044588821863</v>
+        <v>9.443103992167668</v>
       </c>
       <c r="P16" t="n">
-        <v>367.1011099818309</v>
+        <v>367.1888253637761</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -25447,7 +25514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q351"/>
+  <dimension ref="A1:Q352"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55939,6 +56006,93 @@
         </is>
       </c>
     </row>
+    <row r="352">
+      <c r="A352" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>-36.72369963890814,175.71709932514165</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>-36.72373198469008,175.7180168375373</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>-36.723601728862974,175.71889268915808</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>-36.723474537816166,175.71976293434113</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>-36.72330095731612,175.72063180546903</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>-36.723075240967425,175.72148548830356</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>-36.72286156766191,175.72234434253198</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>-36.722651608338566,175.7232038666642</t>
+        </is>
+      </c>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>-36.72246786932443,175.72406194945734</t>
+        </is>
+      </c>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>-36.722157419760656,175.72485171550477</t>
+        </is>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>-36.7218317518626,175.72565184479512</t>
+        </is>
+      </c>
+      <c r="M352" t="inlineStr">
+        <is>
+          <t>-36.72142677476099,175.7263867635382</t>
+        </is>
+      </c>
+      <c r="N352" t="inlineStr">
+        <is>
+          <t>-36.72091936852559,175.7270170899855</t>
+        </is>
+      </c>
+      <c r="O352" t="inlineStr">
+        <is>
+          <t>-36.7204183208663,175.72756986223945</t>
+        </is>
+      </c>
+      <c r="P352" t="inlineStr">
+        <is>
+          <t>-36.7199097410712,175.72823286696502</t>
+        </is>
+      </c>
+      <c r="Q352" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0157/nzd0157.xlsx
+++ b/data/nzd0157/nzd0157.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q352"/>
+  <dimension ref="A1:Q353"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20501,6 +20501,63 @@
         </is>
       </c>
     </row>
+    <row r="353">
+      <c r="A353" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:02+00:00</t>
+        </is>
+      </c>
+      <c r="B353" t="n">
+        <v>387.05</v>
+      </c>
+      <c r="C353" t="n">
+        <v>374.57</v>
+      </c>
+      <c r="D353" t="n">
+        <v>378</v>
+      </c>
+      <c r="E353" t="n">
+        <v>374.99</v>
+      </c>
+      <c r="F353" t="n">
+        <v>369.65</v>
+      </c>
+      <c r="G353" t="n">
+        <v>370.52</v>
+      </c>
+      <c r="H353" t="n">
+        <v>372.21</v>
+      </c>
+      <c r="I353" t="n">
+        <v>374.66</v>
+      </c>
+      <c r="J353" t="n">
+        <v>371.35</v>
+      </c>
+      <c r="K353" t="n">
+        <v>369.18</v>
+      </c>
+      <c r="L353" t="n">
+        <v>362.48</v>
+      </c>
+      <c r="M353" t="n">
+        <v>367.51</v>
+      </c>
+      <c r="N353" t="n">
+        <v>374.01</v>
+      </c>
+      <c r="O353" t="n">
+        <v>383.12</v>
+      </c>
+      <c r="P353" t="n">
+        <v>355.87</v>
+      </c>
+      <c r="Q353" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -20512,7 +20569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B368"/>
+  <dimension ref="A1:B369"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24195,6 +24252,16 @@
       </c>
       <c r="B368" t="n">
         <v>0.55</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B369" t="n">
+        <v>-0.08</v>
       </c>
     </row>
   </sheetData>
@@ -24363,28 +24430,28 @@
         <v>0.0555</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2677937261564768</v>
+        <v>0.2675398470288538</v>
       </c>
       <c r="J2" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K2" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2483491768884566</v>
+        <v>0.249148900121362</v>
       </c>
       <c r="M2" t="n">
-        <v>2.590899837138472</v>
+        <v>2.584761335148324</v>
       </c>
       <c r="N2" t="n">
-        <v>11.77207107936029</v>
+        <v>11.73918948639353</v>
       </c>
       <c r="O2" t="n">
-        <v>3.431045187601045</v>
+        <v>3.42625006185969</v>
       </c>
       <c r="P2" t="n">
-        <v>380.3819408227613</v>
+        <v>380.3846528600675</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -24441,28 +24508,28 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.371762649090603</v>
+        <v>0.370983616836608</v>
       </c>
       <c r="J3" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K3" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2761213909284975</v>
+        <v>0.2764731191113791</v>
       </c>
       <c r="M3" t="n">
-        <v>3.548730892283378</v>
+        <v>3.542565864886126</v>
       </c>
       <c r="N3" t="n">
-        <v>19.65150725290297</v>
+        <v>19.60096881277453</v>
       </c>
       <c r="O3" t="n">
-        <v>4.433002058752395</v>
+        <v>4.427298139133453</v>
       </c>
       <c r="P3" t="n">
-        <v>366.063715564775</v>
+        <v>366.0720374955906</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -24519,28 +24586,28 @@
         <v>0.1281</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3298842997096056</v>
+        <v>0.3310990642113758</v>
       </c>
       <c r="J4" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K4" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2319397114895836</v>
+        <v>0.2342485578934395</v>
       </c>
       <c r="M4" t="n">
-        <v>3.348763966156936</v>
+        <v>3.344838788378457</v>
       </c>
       <c r="N4" t="n">
-        <v>19.54529179163935</v>
+        <v>19.50262728472594</v>
       </c>
       <c r="O4" t="n">
-        <v>4.421005744357198</v>
+        <v>4.416177904560224</v>
       </c>
       <c r="P4" t="n">
-        <v>367.0981636869859</v>
+        <v>367.0851870918714</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -24597,28 +24664,28 @@
         <v>0.09959999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2244353640268314</v>
+        <v>0.2252582874554932</v>
       </c>
       <c r="J5" t="n">
+        <v>352</v>
+      </c>
+      <c r="K5" t="n">
         <v>351</v>
       </c>
-      <c r="K5" t="n">
-        <v>350</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.1389206746499988</v>
+        <v>0.140510364355999</v>
       </c>
       <c r="M5" t="n">
-        <v>3.132356740338393</v>
+        <v>3.127510939386864</v>
       </c>
       <c r="N5" t="n">
-        <v>16.76319262235232</v>
+        <v>16.72124959476488</v>
       </c>
       <c r="O5" t="n">
-        <v>4.094287804045084</v>
+        <v>4.089162456391882</v>
       </c>
       <c r="P5" t="n">
-        <v>367.5939552241982</v>
+        <v>367.5851030600245</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -24675,28 +24742,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1400846446920316</v>
+        <v>0.1414051785230912</v>
       </c>
       <c r="J6" t="n">
+        <v>352</v>
+      </c>
+      <c r="K6" t="n">
         <v>351</v>
       </c>
-      <c r="K6" t="n">
-        <v>350</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.06788790606275696</v>
+        <v>0.06942125135877064</v>
       </c>
       <c r="M6" t="n">
-        <v>2.907458132561673</v>
+        <v>2.904427373261644</v>
       </c>
       <c r="N6" t="n">
-        <v>14.46620695941371</v>
+        <v>14.43996733878982</v>
       </c>
       <c r="O6" t="n">
-        <v>3.803446720990542</v>
+        <v>3.799995702469915</v>
       </c>
       <c r="P6" t="n">
-        <v>363.6211346332915</v>
+        <v>363.6069296880167</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -24753,28 +24820,28 @@
         <v>0.1229</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2155097455205759</v>
+        <v>0.2173679571410893</v>
       </c>
       <c r="J7" t="n">
+        <v>352</v>
+      </c>
+      <c r="K7" t="n">
         <v>351</v>
       </c>
-      <c r="K7" t="n">
-        <v>350</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.1615487118275185</v>
+        <v>0.1644312788067852</v>
       </c>
       <c r="M7" t="n">
-        <v>2.865082833381128</v>
+        <v>2.86415821945285</v>
       </c>
       <c r="N7" t="n">
-        <v>12.94213852276548</v>
+        <v>12.9349179099797</v>
       </c>
       <c r="O7" t="n">
-        <v>3.59751838393711</v>
+        <v>3.596514689248425</v>
       </c>
       <c r="P7" t="n">
-        <v>361.5534937536685</v>
+        <v>361.5335050235371</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -24831,28 +24898,28 @@
         <v>0.074</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2196409433518784</v>
+        <v>0.2234288617794526</v>
       </c>
       <c r="J8" t="n">
+        <v>352</v>
+      </c>
+      <c r="K8" t="n">
         <v>351</v>
       </c>
-      <c r="K8" t="n">
-        <v>350</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.1324250401337432</v>
+        <v>0.136285695567909</v>
       </c>
       <c r="M8" t="n">
-        <v>3.224611483303494</v>
+        <v>3.232308538259442</v>
       </c>
       <c r="N8" t="n">
-        <v>16.96920026105835</v>
+        <v>17.04406857193603</v>
       </c>
       <c r="O8" t="n">
-        <v>4.119368915387204</v>
+        <v>4.128446266083165</v>
       </c>
       <c r="P8" t="n">
-        <v>359.7707233071122</v>
+        <v>359.7299767751389</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -24909,28 +24976,28 @@
         <v>0.09089999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2160852249067947</v>
+        <v>0.2203244721450197</v>
       </c>
       <c r="J9" t="n">
+        <v>352</v>
+      </c>
+      <c r="K9" t="n">
         <v>351</v>
       </c>
-      <c r="K9" t="n">
-        <v>350</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.139013290908317</v>
+        <v>0.143279216919723</v>
       </c>
       <c r="M9" t="n">
-        <v>3.133043093490416</v>
+        <v>3.145420879720151</v>
       </c>
       <c r="N9" t="n">
-        <v>15.52702121625848</v>
+        <v>15.63710921064139</v>
       </c>
       <c r="O9" t="n">
-        <v>3.940434140581274</v>
+        <v>3.954378486012864</v>
       </c>
       <c r="P9" t="n">
-        <v>361.5255503094618</v>
+        <v>361.479948846168</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -24987,28 +25054,28 @@
         <v>0.0915</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1587342112613215</v>
+        <v>0.1584845197709283</v>
       </c>
       <c r="J10" t="n">
+        <v>352</v>
+      </c>
+      <c r="K10" t="n">
         <v>351</v>
       </c>
-      <c r="K10" t="n">
-        <v>350</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.08361738486286252</v>
+        <v>0.0838528714315101</v>
       </c>
       <c r="M10" t="n">
-        <v>3.020969901715064</v>
+        <v>3.013448079458725</v>
       </c>
       <c r="N10" t="n">
-        <v>14.82583683240268</v>
+        <v>14.78413336446617</v>
       </c>
       <c r="O10" t="n">
-        <v>3.850433330471089</v>
+        <v>3.845014091582262</v>
       </c>
       <c r="P10" t="n">
-        <v>367.568208335692</v>
+        <v>367.5708942600305</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -25065,28 +25132,28 @@
         <v>0.0954</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1551973217874049</v>
+        <v>0.1557956798300304</v>
       </c>
       <c r="J11" t="n">
+        <v>352</v>
+      </c>
+      <c r="K11" t="n">
         <v>351</v>
       </c>
-      <c r="K11" t="n">
-        <v>350</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.07595893534622411</v>
+        <v>0.07692997549909597</v>
       </c>
       <c r="M11" t="n">
-        <v>3.175033326356429</v>
+        <v>3.169057016582949</v>
       </c>
       <c r="N11" t="n">
-        <v>15.73181122808873</v>
+        <v>15.69006579001362</v>
       </c>
       <c r="O11" t="n">
-        <v>3.966334734750551</v>
+        <v>3.961068768654948</v>
       </c>
       <c r="P11" t="n">
-        <v>364.0151328327514</v>
+        <v>364.0086963121183</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -25143,28 +25210,28 @@
         <v>0.0953</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1810545770265446</v>
+        <v>0.1786223383693236</v>
       </c>
       <c r="J12" t="n">
+        <v>352</v>
+      </c>
+      <c r="K12" t="n">
         <v>351</v>
       </c>
-      <c r="K12" t="n">
-        <v>350</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.0989868743735024</v>
+        <v>0.09686942964190592</v>
       </c>
       <c r="M12" t="n">
-        <v>3.139597811406075</v>
+        <v>3.140826556154864</v>
       </c>
       <c r="N12" t="n">
-        <v>16.02029104123652</v>
+        <v>16.02544990112001</v>
       </c>
       <c r="O12" t="n">
-        <v>4.002535576511034</v>
+        <v>4.00317997361098</v>
       </c>
       <c r="P12" t="n">
-        <v>361.9076780609382</v>
+        <v>361.9338415837564</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -25221,28 +25288,28 @@
         <v>0.0854</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2700302582411133</v>
+        <v>0.2679375753160421</v>
       </c>
       <c r="J13" t="n">
+        <v>352</v>
+      </c>
+      <c r="K13" t="n">
         <v>351</v>
       </c>
-      <c r="K13" t="n">
-        <v>350</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.1631860621766186</v>
+        <v>0.1616647232016586</v>
       </c>
       <c r="M13" t="n">
-        <v>3.377792385728061</v>
+        <v>3.379130308909736</v>
       </c>
       <c r="N13" t="n">
-        <v>20.075602349441</v>
+        <v>20.05601352189847</v>
       </c>
       <c r="O13" t="n">
-        <v>4.480580581737259</v>
+        <v>4.478394078450273</v>
       </c>
       <c r="P13" t="n">
-        <v>363.9835594646818</v>
+        <v>364.0060703960408</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -25299,28 +25366,28 @@
         <v>0.0863</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3101444035328778</v>
+        <v>0.3095970239548821</v>
       </c>
       <c r="J14" t="n">
+        <v>352</v>
+      </c>
+      <c r="K14" t="n">
         <v>351</v>
       </c>
-      <c r="K14" t="n">
-        <v>350</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.1607666603942077</v>
+        <v>0.1611211900999744</v>
       </c>
       <c r="M14" t="n">
-        <v>4.010772829208173</v>
+        <v>4.001878364273131</v>
       </c>
       <c r="N14" t="n">
-        <v>26.95954229041427</v>
+        <v>26.88530744707121</v>
       </c>
       <c r="O14" t="n">
-        <v>5.19225791832554</v>
+        <v>5.185104381501997</v>
       </c>
       <c r="P14" t="n">
-        <v>366.7267106142261</v>
+        <v>366.7325987609491</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -25377,28 +25444,28 @@
         <v>0.0477</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5426803137777474</v>
+        <v>0.5419541849223912</v>
       </c>
       <c r="J15" t="n">
+        <v>352</v>
+      </c>
+      <c r="K15" t="n">
         <v>351</v>
       </c>
-      <c r="K15" t="n">
-        <v>350</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.1973802833159548</v>
+        <v>0.1979362213021307</v>
       </c>
       <c r="M15" t="n">
-        <v>5.815554417427907</v>
+        <v>5.802323605147147</v>
       </c>
       <c r="N15" t="n">
-        <v>64.29720133090379</v>
+        <v>64.11854619615377</v>
       </c>
       <c r="O15" t="n">
-        <v>8.018553568499982</v>
+        <v>8.007405709476307</v>
       </c>
       <c r="P15" t="n">
-        <v>369.9724207019325</v>
+        <v>369.9802316496039</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -25455,28 +25522,28 @@
         <v>0.0274</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.00376220284696303</v>
+        <v>-0.0101959901669348</v>
       </c>
       <c r="J16" t="n">
+        <v>352</v>
+      </c>
+      <c r="K16" t="n">
         <v>351</v>
       </c>
-      <c r="K16" t="n">
-        <v>350</v>
-      </c>
       <c r="L16" t="n">
-        <v>8.522147533107649e-06</v>
+        <v>6.273115867683199e-05</v>
       </c>
       <c r="M16" t="n">
-        <v>6.741444108528491</v>
+        <v>6.747414642807344</v>
       </c>
       <c r="N16" t="n">
-        <v>89.17221300689293</v>
+        <v>89.27362121061562</v>
       </c>
       <c r="O16" t="n">
-        <v>9.443103992167668</v>
+        <v>9.448471898175685</v>
       </c>
       <c r="P16" t="n">
-        <v>367.1888253637761</v>
+        <v>367.258033432998</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -25514,7 +25581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q352"/>
+  <dimension ref="A1:Q353"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56093,6 +56160,93 @@
         </is>
       </c>
     </row>
+    <row r="353">
+      <c r="A353" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:02+00:00</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>-36.723720069588026,175.71710360485304</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>-36.72372452306214,175.71801527445376</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>-36.72358929949982,175.71888943926479</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>-36.72345621035883,175.71975626521774</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>-36.723288993257086,175.72062684990192</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>-36.72306650382785,175.72148195501367</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>-36.722846613852354,175.72233850658418</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>-36.72262485387028,175.72319354191993</t>
+        </is>
+      </c>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>-36.72245723447451,175.72405641431212</t>
+        </is>
+      </c>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>-36.722154845045296,175.72484986967032</t>
+        </is>
+      </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>-36.72184143560781,175.7256596202178</t>
+        </is>
+      </c>
+      <c r="M353" t="inlineStr">
+        <is>
+          <t>-36.72141657700339,175.72637717084905</t>
+        </is>
+      </c>
+      <c r="N353" t="inlineStr">
+        <is>
+          <t>-36.72092299052034,175.72702112360676</t>
+        </is>
+      </c>
+      <c r="O353" t="inlineStr">
+        <is>
+          <t>-36.720419659971746,175.72757224919263</t>
+        </is>
+      </c>
+      <c r="P353" t="inlineStr">
+        <is>
+          <t>-36.71989932024548,175.72820298798206</t>
+        </is>
+      </c>
+      <c r="Q353" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0157/nzd0157.xlsx
+++ b/data/nzd0157/nzd0157.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q353"/>
+  <dimension ref="A1:Q354"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20558,6 +20558,63 @@
         </is>
       </c>
     </row>
+    <row r="354">
+      <c r="A354" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B354" t="n">
+        <v>387.41</v>
+      </c>
+      <c r="C354" t="n">
+        <v>375.66</v>
+      </c>
+      <c r="D354" t="n">
+        <v>378.07</v>
+      </c>
+      <c r="E354" t="n">
+        <v>375.36</v>
+      </c>
+      <c r="F354" t="n">
+        <v>370.03</v>
+      </c>
+      <c r="G354" t="n">
+        <v>370.24</v>
+      </c>
+      <c r="H354" t="n">
+        <v>371.45</v>
+      </c>
+      <c r="I354" t="n">
+        <v>373.66</v>
+      </c>
+      <c r="J354" t="n">
+        <v>371.3</v>
+      </c>
+      <c r="K354" t="n">
+        <v>368.78</v>
+      </c>
+      <c r="L354" t="n">
+        <v>362.59</v>
+      </c>
+      <c r="M354" t="n">
+        <v>367.04</v>
+      </c>
+      <c r="N354" t="n">
+        <v>373.67</v>
+      </c>
+      <c r="O354" t="n">
+        <v>381.61</v>
+      </c>
+      <c r="P354" t="n">
+        <v>358.73</v>
+      </c>
+      <c r="Q354" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -20569,7 +20626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B369"/>
+  <dimension ref="A1:B370"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24262,6 +24319,16 @@
       </c>
       <c r="B369" t="n">
         <v>-0.08</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B370" t="n">
+        <v>-0.46</v>
       </c>
     </row>
   </sheetData>
@@ -24430,28 +24497,28 @@
         <v>0.0555</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2675398470288538</v>
+        <v>0.2674767627340704</v>
       </c>
       <c r="J2" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K2" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L2" t="n">
-        <v>0.249148900121362</v>
+        <v>0.2502308863343983</v>
       </c>
       <c r="M2" t="n">
-        <v>2.584761335148324</v>
+        <v>2.577739426950205</v>
       </c>
       <c r="N2" t="n">
-        <v>11.73918948639353</v>
+        <v>11.70596865415617</v>
       </c>
       <c r="O2" t="n">
-        <v>3.42625006185969</v>
+        <v>3.42139864005295</v>
       </c>
       <c r="P2" t="n">
-        <v>380.3846528600675</v>
+        <v>380.3853292688579</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -24508,28 +24575,28 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.370983616836608</v>
+        <v>0.3708156451193993</v>
       </c>
       <c r="J3" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K3" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2764731191113791</v>
+        <v>0.2775409112430185</v>
       </c>
       <c r="M3" t="n">
-        <v>3.542565864886126</v>
+        <v>3.533365709186752</v>
       </c>
       <c r="N3" t="n">
-        <v>19.60096881277453</v>
+        <v>19.54568773364719</v>
       </c>
       <c r="O3" t="n">
-        <v>4.427298139133453</v>
+        <v>4.421050523760975</v>
       </c>
       <c r="P3" t="n">
-        <v>366.0720374955906</v>
+        <v>366.0738385388842</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -24586,28 +24653,28 @@
         <v>0.1281</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3310990642113758</v>
+        <v>0.3323248439413707</v>
       </c>
       <c r="J4" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K4" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2342485578934395</v>
+        <v>0.2365827027137596</v>
       </c>
       <c r="M4" t="n">
-        <v>3.344838788378457</v>
+        <v>3.340942671133996</v>
       </c>
       <c r="N4" t="n">
-        <v>19.50262728472594</v>
+        <v>19.4604659467263</v>
       </c>
       <c r="O4" t="n">
-        <v>4.416177904560224</v>
+        <v>4.411401811978399</v>
       </c>
       <c r="P4" t="n">
-        <v>367.0851870918714</v>
+        <v>367.072043912777</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -24664,28 +24731,28 @@
         <v>0.09959999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2252582874554932</v>
+        <v>0.2262713903081288</v>
       </c>
       <c r="J5" t="n">
+        <v>353</v>
+      </c>
+      <c r="K5" t="n">
         <v>352</v>
       </c>
-      <c r="K5" t="n">
-        <v>351</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.140510364355999</v>
+        <v>0.1422982969041316</v>
       </c>
       <c r="M5" t="n">
-        <v>3.127510939386864</v>
+        <v>3.123643968198854</v>
       </c>
       <c r="N5" t="n">
-        <v>16.72124959476488</v>
+        <v>16.68255362461604</v>
       </c>
       <c r="O5" t="n">
-        <v>4.089162456391882</v>
+        <v>4.084428188206526</v>
       </c>
       <c r="P5" t="n">
-        <v>367.5851030600245</v>
+        <v>367.574164790659</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -24742,28 +24809,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1414051785230912</v>
+        <v>0.1429242217914709</v>
       </c>
       <c r="J6" t="n">
+        <v>353</v>
+      </c>
+      <c r="K6" t="n">
         <v>352</v>
       </c>
-      <c r="K6" t="n">
-        <v>351</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.06942125135877064</v>
+        <v>0.07113806084893315</v>
       </c>
       <c r="M6" t="n">
-        <v>2.904427373261644</v>
+        <v>2.902144124634955</v>
       </c>
       <c r="N6" t="n">
-        <v>14.43996733878982</v>
+        <v>14.41874582637075</v>
       </c>
       <c r="O6" t="n">
-        <v>3.799995702469915</v>
+        <v>3.797202368372108</v>
       </c>
       <c r="P6" t="n">
-        <v>363.6069296880167</v>
+        <v>363.5905288809278</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -24820,28 +24887,28 @@
         <v>0.1229</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2173679571410893</v>
+        <v>0.2190383516718926</v>
       </c>
       <c r="J7" t="n">
+        <v>353</v>
+      </c>
+      <c r="K7" t="n">
         <v>352</v>
       </c>
-      <c r="K7" t="n">
-        <v>351</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.1644312788067852</v>
+        <v>0.1671608406766185</v>
       </c>
       <c r="M7" t="n">
-        <v>2.86415821945285</v>
+        <v>2.862449258043767</v>
       </c>
       <c r="N7" t="n">
-        <v>12.9349179099797</v>
+        <v>12.92211448388086</v>
       </c>
       <c r="O7" t="n">
-        <v>3.596514689248425</v>
+        <v>3.594734271664716</v>
       </c>
       <c r="P7" t="n">
-        <v>361.5335050235371</v>
+        <v>361.5154701070654</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -24898,28 +24965,28 @@
         <v>0.074</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2234288617794526</v>
+        <v>0.226730459124572</v>
       </c>
       <c r="J8" t="n">
+        <v>353</v>
+      </c>
+      <c r="K8" t="n">
         <v>352</v>
       </c>
-      <c r="K8" t="n">
-        <v>351</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.136285695567909</v>
+        <v>0.1398712456386578</v>
       </c>
       <c r="M8" t="n">
-        <v>3.232308538259442</v>
+        <v>3.237788089861141</v>
       </c>
       <c r="N8" t="n">
-        <v>17.04406857193603</v>
+        <v>17.08918800008208</v>
       </c>
       <c r="O8" t="n">
-        <v>4.128446266083165</v>
+        <v>4.133907110722504</v>
       </c>
       <c r="P8" t="n">
-        <v>359.7299767751389</v>
+        <v>359.6943300873389</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -24976,28 +25043,28 @@
         <v>0.09089999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2203244721450197</v>
+        <v>0.2239369506732712</v>
       </c>
       <c r="J9" t="n">
+        <v>353</v>
+      </c>
+      <c r="K9" t="n">
         <v>352</v>
       </c>
-      <c r="K9" t="n">
-        <v>351</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.143279216919723</v>
+        <v>0.1472083066979692</v>
       </c>
       <c r="M9" t="n">
-        <v>3.145420879720151</v>
+        <v>3.15461814681851</v>
       </c>
       <c r="N9" t="n">
-        <v>15.63710921064139</v>
+        <v>15.7046706582052</v>
       </c>
       <c r="O9" t="n">
-        <v>3.954378486012864</v>
+        <v>3.96291189129978</v>
       </c>
       <c r="P9" t="n">
-        <v>361.479948846168</v>
+        <v>361.4409456362607</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -25054,28 +25121,28 @@
         <v>0.0915</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1584845197709283</v>
+        <v>0.158198858246326</v>
       </c>
       <c r="J10" t="n">
+        <v>353</v>
+      </c>
+      <c r="K10" t="n">
         <v>352</v>
       </c>
-      <c r="K10" t="n">
-        <v>351</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.0838528714315101</v>
+        <v>0.08405468958448015</v>
       </c>
       <c r="M10" t="n">
-        <v>3.013448079458725</v>
+        <v>3.006114241743532</v>
       </c>
       <c r="N10" t="n">
-        <v>14.78413336446617</v>
+        <v>14.74283323541905</v>
       </c>
       <c r="O10" t="n">
-        <v>3.845014091582262</v>
+        <v>3.839639727294613</v>
       </c>
       <c r="P10" t="n">
-        <v>367.5708942600305</v>
+        <v>367.5739784905164</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -25132,28 +25199,28 @@
         <v>0.0954</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1557956798300304</v>
+        <v>0.1561470441015347</v>
       </c>
       <c r="J11" t="n">
+        <v>353</v>
+      </c>
+      <c r="K11" t="n">
         <v>352</v>
       </c>
-      <c r="K11" t="n">
-        <v>351</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.07692997549909597</v>
+        <v>0.07769451673975292</v>
       </c>
       <c r="M11" t="n">
-        <v>3.169057016582949</v>
+        <v>3.161837275798466</v>
       </c>
       <c r="N11" t="n">
-        <v>15.69006579001362</v>
+        <v>15.64655115103593</v>
       </c>
       <c r="O11" t="n">
-        <v>3.961068768654948</v>
+        <v>3.955572164812055</v>
       </c>
       <c r="P11" t="n">
-        <v>364.0086963121183</v>
+        <v>364.0049027021831</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -25210,28 +25277,28 @@
         <v>0.0953</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1786223383693236</v>
+        <v>0.1762729842377327</v>
       </c>
       <c r="J12" t="n">
+        <v>353</v>
+      </c>
+      <c r="K12" t="n">
         <v>352</v>
       </c>
-      <c r="K12" t="n">
-        <v>351</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.09686942964190592</v>
+        <v>0.09486213725125214</v>
       </c>
       <c r="M12" t="n">
-        <v>3.140826556154864</v>
+        <v>3.141715158601357</v>
       </c>
       <c r="N12" t="n">
-        <v>16.02544990112001</v>
+        <v>16.02728684873817</v>
       </c>
       <c r="O12" t="n">
-        <v>4.00317997361098</v>
+        <v>4.003409403088594</v>
       </c>
       <c r="P12" t="n">
-        <v>361.9338415837564</v>
+        <v>361.9592070915716</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -25288,28 +25355,28 @@
         <v>0.0854</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2679375753160421</v>
+        <v>0.2655865084398217</v>
       </c>
       <c r="J13" t="n">
+        <v>353</v>
+      </c>
+      <c r="K13" t="n">
         <v>352</v>
       </c>
-      <c r="K13" t="n">
-        <v>351</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.1616647232016586</v>
+        <v>0.1598144383914015</v>
       </c>
       <c r="M13" t="n">
-        <v>3.379130308909736</v>
+        <v>3.381881496657559</v>
       </c>
       <c r="N13" t="n">
-        <v>20.05601352189847</v>
+        <v>20.04646908890911</v>
       </c>
       <c r="O13" t="n">
-        <v>4.478394078450273</v>
+        <v>4.477328342763027</v>
       </c>
       <c r="P13" t="n">
-        <v>364.0060703960408</v>
+        <v>364.031454396018</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -25366,28 +25433,28 @@
         <v>0.0863</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3095970239548821</v>
+        <v>0.3088456802931226</v>
       </c>
       <c r="J14" t="n">
+        <v>353</v>
+      </c>
+      <c r="K14" t="n">
         <v>352</v>
       </c>
-      <c r="K14" t="n">
-        <v>351</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.1611211900999744</v>
+        <v>0.1612888109322305</v>
       </c>
       <c r="M14" t="n">
-        <v>4.001878364273131</v>
+        <v>3.993943180501658</v>
       </c>
       <c r="N14" t="n">
-        <v>26.88530744707121</v>
+        <v>26.81377298516876</v>
       </c>
       <c r="O14" t="n">
-        <v>5.185104381501997</v>
+        <v>5.178201713449251</v>
       </c>
       <c r="P14" t="n">
-        <v>366.7325987609491</v>
+        <v>366.7407108685569</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -25444,28 +25511,28 @@
         <v>0.0477</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5419541849223912</v>
+        <v>0.5403410597862748</v>
       </c>
       <c r="J15" t="n">
+        <v>353</v>
+      </c>
+      <c r="K15" t="n">
         <v>352</v>
       </c>
-      <c r="K15" t="n">
-        <v>351</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.1979362213021307</v>
+        <v>0.1979312743392813</v>
       </c>
       <c r="M15" t="n">
-        <v>5.802323605147147</v>
+        <v>5.793175557199522</v>
       </c>
       <c r="N15" t="n">
-        <v>64.11854619615377</v>
+        <v>63.9587210762913</v>
       </c>
       <c r="O15" t="n">
-        <v>8.007405709476307</v>
+        <v>7.997419651130688</v>
       </c>
       <c r="P15" t="n">
-        <v>369.9802316496039</v>
+        <v>369.9976482398476</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -25522,28 +25589,28 @@
         <v>0.0274</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.0101959901669348</v>
+        <v>-0.01492197504627696</v>
       </c>
       <c r="J16" t="n">
+        <v>353</v>
+      </c>
+      <c r="K16" t="n">
         <v>352</v>
       </c>
-      <c r="K16" t="n">
-        <v>351</v>
-      </c>
       <c r="L16" t="n">
-        <v>6.273115867683199e-05</v>
+        <v>0.000134908418982449</v>
       </c>
       <c r="M16" t="n">
-        <v>6.747414642807344</v>
+        <v>6.746699344277617</v>
       </c>
       <c r="N16" t="n">
-        <v>89.27362121061562</v>
+        <v>89.21166415296528</v>
       </c>
       <c r="O16" t="n">
-        <v>9.448471898175685</v>
+        <v>9.445192647742305</v>
       </c>
       <c r="P16" t="n">
-        <v>367.258033432998</v>
+        <v>367.3090589488112</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -25581,7 +25648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q353"/>
+  <dimension ref="A1:Q354"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56247,6 +56314,93 @@
         </is>
       </c>
     </row>
+    <row r="354">
+      <c r="A354" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>-36.72371687174252,175.71710293498498</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>-36.723714840711516,175.71801324616726</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>-36.72358868243922,175.71888927792259</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>-36.72345301169878,175.7197551012673</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>-36.723285745869596,175.7206255048197</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>-36.72306890225833,175.72148292493628</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>-36.7228531454014,175.72234105561856</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>-36.72263345659334,175.72319686177255</t>
+        </is>
+      </c>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>-36.722457649898345,175.7240566305287</t>
+        </is>
+      </c>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>-36.72215796591239,175.72485210704545</t>
+        </is>
+      </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>-36.72184060341099,175.72565895201734</t>
+        </is>
+      </c>
+      <c r="M354" t="inlineStr">
+        <is>
+          <t>-36.721419952317625,175.72638034589377</t>
+        </is>
+      </c>
+      <c r="N354" t="inlineStr">
+        <is>
+          <t>-36.720925271035476,175.72702366329443</t>
+        </is>
+      </c>
+      <c r="O354" t="inlineStr">
+        <is>
+          <t>-36.72042743708318,175.72758611188368</t>
+        </is>
+      </c>
+      <c r="P354" t="inlineStr">
+        <is>
+          <t>-36.71988907846411,175.72817362239118</t>
+        </is>
+      </c>
+      <c r="Q354" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0157/nzd0157.xlsx
+++ b/data/nzd0157/nzd0157.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q354"/>
+  <dimension ref="A1:Q357"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20615,6 +20615,177 @@
         </is>
       </c>
     </row>
+    <row r="355">
+      <c r="A355" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:29+00:00</t>
+        </is>
+      </c>
+      <c r="B355" t="n">
+        <v>388.33</v>
+      </c>
+      <c r="C355" t="n">
+        <v>376.83</v>
+      </c>
+      <c r="D355" t="n">
+        <v>378.33</v>
+      </c>
+      <c r="E355" t="n">
+        <v>375.82</v>
+      </c>
+      <c r="F355" t="n">
+        <v>369.24</v>
+      </c>
+      <c r="G355" t="n">
+        <v>370.01</v>
+      </c>
+      <c r="H355" t="n">
+        <v>370.88</v>
+      </c>
+      <c r="I355" t="n">
+        <v>374.08</v>
+      </c>
+      <c r="J355" t="n">
+        <v>370.99</v>
+      </c>
+      <c r="K355" t="n">
+        <v>369.89</v>
+      </c>
+      <c r="L355" t="n">
+        <v>362.46</v>
+      </c>
+      <c r="M355" t="n">
+        <v>366.68</v>
+      </c>
+      <c r="N355" t="n">
+        <v>373.55</v>
+      </c>
+      <c r="O355" t="n">
+        <v>380.08</v>
+      </c>
+      <c r="P355" t="n">
+        <v>362.52</v>
+      </c>
+      <c r="Q355" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:04:44+00:00</t>
+        </is>
+      </c>
+      <c r="B356" t="n">
+        <v>389.97</v>
+      </c>
+      <c r="C356" t="n">
+        <v>383.98</v>
+      </c>
+      <c r="D356" t="n">
+        <v>380.93</v>
+      </c>
+      <c r="E356" t="n">
+        <v>380.02</v>
+      </c>
+      <c r="F356" t="n">
+        <v>370.12</v>
+      </c>
+      <c r="G356" t="n">
+        <v>371.31</v>
+      </c>
+      <c r="H356" t="n">
+        <v>372.05</v>
+      </c>
+      <c r="I356" t="n">
+        <v>371.05</v>
+      </c>
+      <c r="J356" t="n">
+        <v>372.37</v>
+      </c>
+      <c r="K356" t="n">
+        <v>371.28</v>
+      </c>
+      <c r="L356" t="n">
+        <v>364.57</v>
+      </c>
+      <c r="M356" t="n">
+        <v>368.2</v>
+      </c>
+      <c r="N356" t="n">
+        <v>372.69</v>
+      </c>
+      <c r="O356" t="n">
+        <v>376.77</v>
+      </c>
+      <c r="P356" t="n">
+        <v>367.84</v>
+      </c>
+      <c r="Q356" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:05:20+00:00</t>
+        </is>
+      </c>
+      <c r="B357" t="n">
+        <v>389.67</v>
+      </c>
+      <c r="C357" t="n">
+        <v>383.06</v>
+      </c>
+      <c r="D357" t="n">
+        <v>380.4</v>
+      </c>
+      <c r="E357" t="n">
+        <v>380</v>
+      </c>
+      <c r="F357" t="n">
+        <v>369.07</v>
+      </c>
+      <c r="G357" t="n">
+        <v>370.43</v>
+      </c>
+      <c r="H357" t="n">
+        <v>370.75</v>
+      </c>
+      <c r="I357" t="n">
+        <v>368.94</v>
+      </c>
+      <c r="J357" t="n">
+        <v>371.54</v>
+      </c>
+      <c r="K357" t="n">
+        <v>369.96</v>
+      </c>
+      <c r="L357" t="n">
+        <v>364.52</v>
+      </c>
+      <c r="M357" t="n">
+        <v>367.6</v>
+      </c>
+      <c r="N357" t="n">
+        <v>371.51</v>
+      </c>
+      <c r="O357" t="n">
+        <v>376.39</v>
+      </c>
+      <c r="P357" t="n">
+        <v>369.09</v>
+      </c>
+      <c r="Q357" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -20626,7 +20797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B370"/>
+  <dimension ref="A1:B373"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24329,6 +24500,36 @@
       </c>
       <c r="B370" t="n">
         <v>-0.46</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B371" t="n">
+        <v>-0.09</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B372" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B373" t="n">
+        <v>-0.59</v>
       </c>
     </row>
   </sheetData>
@@ -24497,28 +24698,28 @@
         <v>0.0555</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2674767627340704</v>
+        <v>0.2704469294764054</v>
       </c>
       <c r="J2" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="K2" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2502308863343983</v>
+        <v>0.2575053997478758</v>
       </c>
       <c r="M2" t="n">
-        <v>2.577739426950205</v>
+        <v>2.571142679654841</v>
       </c>
       <c r="N2" t="n">
-        <v>11.70596865415617</v>
+        <v>11.63700447881723</v>
       </c>
       <c r="O2" t="n">
-        <v>3.42139864005295</v>
+        <v>3.411305392194786</v>
       </c>
       <c r="P2" t="n">
-        <v>380.3853292688579</v>
+        <v>380.3532454184222</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -24575,28 +24776,28 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3708156451193993</v>
+        <v>0.3796966116751259</v>
       </c>
       <c r="J3" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="K3" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2775409112430185</v>
+        <v>0.2877210396803278</v>
       </c>
       <c r="M3" t="n">
-        <v>3.533365709186752</v>
+        <v>3.54694519967774</v>
       </c>
       <c r="N3" t="n">
-        <v>19.54568773364719</v>
+        <v>19.69346205299707</v>
       </c>
       <c r="O3" t="n">
-        <v>4.421050523760975</v>
+        <v>4.437731633728776</v>
       </c>
       <c r="P3" t="n">
-        <v>366.0738385388842</v>
+        <v>365.9778848903743</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -24653,28 +24854,28 @@
         <v>0.1281</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3323248439413707</v>
+        <v>0.3388932983688552</v>
       </c>
       <c r="J4" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="K4" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2365827027137596</v>
+        <v>0.2459235571048186</v>
       </c>
       <c r="M4" t="n">
-        <v>3.340942671133996</v>
+        <v>3.342512439783084</v>
       </c>
       <c r="N4" t="n">
-        <v>19.4604659467263</v>
+        <v>19.43172409599416</v>
       </c>
       <c r="O4" t="n">
-        <v>4.411401811978399</v>
+        <v>4.408142930531422</v>
       </c>
       <c r="P4" t="n">
-        <v>367.072043912777</v>
+        <v>367.0010996166304</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -24731,28 +24932,28 @@
         <v>0.09959999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2262713903081288</v>
+        <v>0.2347122290314982</v>
       </c>
       <c r="J5" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="K5" t="n">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1422982969041316</v>
+        <v>0.1520947631400631</v>
       </c>
       <c r="M5" t="n">
-        <v>3.123643968198854</v>
+        <v>3.138428941923333</v>
       </c>
       <c r="N5" t="n">
-        <v>16.68255362461604</v>
+        <v>16.77728883192028</v>
       </c>
       <c r="O5" t="n">
-        <v>4.084428188206526</v>
+        <v>4.09600889060562</v>
       </c>
       <c r="P5" t="n">
-        <v>367.574164790659</v>
+        <v>367.4823563649284</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -24809,28 +25010,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1429242217914709</v>
+        <v>0.1464129417959582</v>
       </c>
       <c r="J6" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="K6" t="n">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07113806084893315</v>
+        <v>0.07553006252031047</v>
       </c>
       <c r="M6" t="n">
-        <v>2.902144124634955</v>
+        <v>2.891173485780401</v>
       </c>
       <c r="N6" t="n">
-        <v>14.41874582637075</v>
+        <v>14.33339836024875</v>
       </c>
       <c r="O6" t="n">
-        <v>3.797202368372108</v>
+        <v>3.785947485141435</v>
       </c>
       <c r="P6" t="n">
-        <v>363.5905288809278</v>
+        <v>363.552599034231</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -24887,28 +25088,28 @@
         <v>0.1229</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2190383516718926</v>
+        <v>0.224460933569556</v>
       </c>
       <c r="J7" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="K7" t="n">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1671608406766185</v>
+        <v>0.1758496022852807</v>
       </c>
       <c r="M7" t="n">
-        <v>2.862449258043767</v>
+        <v>2.858579419682135</v>
       </c>
       <c r="N7" t="n">
-        <v>12.92211448388086</v>
+        <v>12.89923338974516</v>
       </c>
       <c r="O7" t="n">
-        <v>3.594734271664716</v>
+        <v>3.591550276655634</v>
       </c>
       <c r="P7" t="n">
-        <v>361.5154701070654</v>
+        <v>361.4565100229854</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -24965,28 +25166,28 @@
         <v>0.074</v>
       </c>
       <c r="I8" t="n">
-        <v>0.226730459124572</v>
+        <v>0.2359776536329415</v>
       </c>
       <c r="J8" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="K8" t="n">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1398712456386578</v>
+        <v>0.1503437591635388</v>
       </c>
       <c r="M8" t="n">
-        <v>3.237788089861141</v>
+        <v>3.251036327251109</v>
       </c>
       <c r="N8" t="n">
-        <v>17.08918800008208</v>
+        <v>17.19162354171575</v>
       </c>
       <c r="O8" t="n">
-        <v>4.133907110722504</v>
+        <v>4.14627827596216</v>
       </c>
       <c r="P8" t="n">
-        <v>359.6943300873389</v>
+        <v>359.5937929213716</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -25043,28 +25244,28 @@
         <v>0.09089999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2239369506732712</v>
+        <v>0.2305644049978862</v>
       </c>
       <c r="J9" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="K9" t="n">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1472083066979692</v>
+        <v>0.155799946177791</v>
       </c>
       <c r="M9" t="n">
-        <v>3.15461814681851</v>
+        <v>3.16174421397743</v>
       </c>
       <c r="N9" t="n">
-        <v>15.7046706582052</v>
+        <v>15.7354759195712</v>
       </c>
       <c r="O9" t="n">
-        <v>3.96291189129978</v>
+        <v>3.96679668240902</v>
       </c>
       <c r="P9" t="n">
-        <v>361.4409456362607</v>
+        <v>361.3689359066347</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -25121,28 +25322,28 @@
         <v>0.0915</v>
       </c>
       <c r="I10" t="n">
-        <v>0.158198858246326</v>
+        <v>0.1578844368100256</v>
       </c>
       <c r="J10" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="K10" t="n">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="L10" t="n">
-        <v>0.08405468958448015</v>
+        <v>0.08519987588368816</v>
       </c>
       <c r="M10" t="n">
-        <v>3.006114241743532</v>
+        <v>2.985146126467936</v>
       </c>
       <c r="N10" t="n">
-        <v>14.74283323541905</v>
+        <v>14.62120566604209</v>
       </c>
       <c r="O10" t="n">
-        <v>3.839639727294613</v>
+        <v>3.823768516273192</v>
       </c>
       <c r="P10" t="n">
-        <v>367.5739784905164</v>
+        <v>367.5773903288945</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -25199,28 +25400,28 @@
         <v>0.0954</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1561470441015347</v>
+        <v>0.159859723582522</v>
       </c>
       <c r="J11" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="K11" t="n">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="L11" t="n">
-        <v>0.07769451673975292</v>
+        <v>0.08234667367901205</v>
       </c>
       <c r="M11" t="n">
-        <v>3.161837275798466</v>
+        <v>3.15372458020981</v>
       </c>
       <c r="N11" t="n">
-        <v>15.64655115103593</v>
+        <v>15.557076467002</v>
       </c>
       <c r="O11" t="n">
-        <v>3.955572164812055</v>
+        <v>3.944245994737397</v>
       </c>
       <c r="P11" t="n">
-        <v>364.0049027021831</v>
+        <v>363.9645352032405</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -25277,28 +25478,28 @@
         <v>0.0953</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1762729842377327</v>
+        <v>0.1714620715986921</v>
       </c>
       <c r="J12" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="K12" t="n">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="L12" t="n">
-        <v>0.09486213725125214</v>
+        <v>0.09139670222770657</v>
       </c>
       <c r="M12" t="n">
-        <v>3.141715158601357</v>
+        <v>3.135151171979742</v>
       </c>
       <c r="N12" t="n">
-        <v>16.02728684873817</v>
+        <v>15.96603969882251</v>
       </c>
       <c r="O12" t="n">
-        <v>4.003409403088594</v>
+        <v>3.995752707416028</v>
       </c>
       <c r="P12" t="n">
-        <v>361.9592070915716</v>
+        <v>362.0114923888731</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -25355,28 +25556,28 @@
         <v>0.0854</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2655865084398217</v>
+        <v>0.2593712127634435</v>
       </c>
       <c r="J13" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="K13" t="n">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1598144383914015</v>
+        <v>0.1552895880160808</v>
       </c>
       <c r="M13" t="n">
-        <v>3.381881496657559</v>
+        <v>3.385199953313743</v>
       </c>
       <c r="N13" t="n">
-        <v>20.04646908890911</v>
+        <v>19.99062368192909</v>
       </c>
       <c r="O13" t="n">
-        <v>4.477328342763027</v>
+        <v>4.471087527876086</v>
       </c>
       <c r="P13" t="n">
-        <v>364.031454396018</v>
+        <v>364.099017840108</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -25433,28 +25634,28 @@
         <v>0.0863</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3088456802931226</v>
+        <v>0.3046956723872619</v>
       </c>
       <c r="J14" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="K14" t="n">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1612888109322305</v>
+        <v>0.1599189019317211</v>
       </c>
       <c r="M14" t="n">
-        <v>3.993943180501658</v>
+        <v>3.978646862581065</v>
       </c>
       <c r="N14" t="n">
-        <v>26.81377298516876</v>
+        <v>26.64227303493353</v>
       </c>
       <c r="O14" t="n">
-        <v>5.178201713449251</v>
+        <v>5.161615351315277</v>
       </c>
       <c r="P14" t="n">
-        <v>366.7407108685569</v>
+        <v>366.7858470949799</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -25511,28 +25712,28 @@
         <v>0.0477</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5403410597862748</v>
+        <v>0.5288816669204726</v>
       </c>
       <c r="J15" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="K15" t="n">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1979312743392813</v>
+        <v>0.1931868166892452</v>
       </c>
       <c r="M15" t="n">
-        <v>5.793175557199522</v>
+        <v>5.796282493817581</v>
       </c>
       <c r="N15" t="n">
-        <v>63.9587210762913</v>
+        <v>63.81603457455267</v>
       </c>
       <c r="O15" t="n">
-        <v>7.997419651130688</v>
+        <v>7.988493886494042</v>
       </c>
       <c r="P15" t="n">
-        <v>369.9976482398476</v>
+        <v>370.1222696050282</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -25589,28 +25790,28 @@
         <v>0.0274</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.01492197504627696</v>
+        <v>-0.01563928132118662</v>
       </c>
       <c r="J16" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="K16" t="n">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="L16" t="n">
-        <v>0.000134908418982449</v>
+        <v>0.000150905525866607</v>
       </c>
       <c r="M16" t="n">
-        <v>6.746699344277617</v>
+        <v>6.710152652863343</v>
       </c>
       <c r="N16" t="n">
-        <v>89.21166415296528</v>
+        <v>88.52790503451905</v>
       </c>
       <c r="O16" t="n">
-        <v>9.445192647742305</v>
+        <v>9.408926880070812</v>
       </c>
       <c r="P16" t="n">
-        <v>367.3090589488112</v>
+        <v>367.3167982988438</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -25648,7 +25849,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q354"/>
+  <dimension ref="A1:Q357"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56401,6 +56602,267 @@
         </is>
       </c>
     </row>
+    <row r="355">
+      <c r="A355" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:29+00:00</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>-36.72370869947057,175.7171012231003</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>-36.72370444772959,175.7180110690164</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>-36.7235863904999,175.71888867865164</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>-36.723449034986245,175.71975365419397</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>-36.72329249701727,175.72062830117497</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>-36.723070872397656,175.72148372165853</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>-36.722858044063145,175.72234296739464</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>-36.72262984344967,175.72319546743435</t>
+        </is>
+      </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>-36.72246022552608,175.72405797107155</t>
+        </is>
+      </c>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>-36.72214930550606,175.72484589832993</t>
+        </is>
+      </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>-36.721841586916334,175.7256597417088</t>
+        </is>
+      </c>
+      <c r="M355" t="inlineStr">
+        <is>
+          <t>-36.72142253766462,175.72638277784307</t>
+        </is>
+      </c>
+      <c r="N355" t="inlineStr">
+        <is>
+          <t>-36.72092607592317,175.7270245596548</t>
+        </is>
+      </c>
+      <c r="O355" t="inlineStr">
+        <is>
+          <t>-36.720435317200945,175.72760015818938</t>
+        </is>
+      </c>
+      <c r="P355" t="inlineStr">
+        <is>
+          <t>-36.71987550630155,175.72813470786085</t>
+        </is>
+      </c>
+      <c r="Q355" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:04:44+00:00</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>-36.72369413150743,175.71709817148079</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>-36.723640935060494,175.71799776422006</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>-36.72356347110636,175.71888268594415</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>-36.723412725870624,175.7197404417925</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>-36.72328497675151,175.72062518624762</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>-36.72305973682749,175.7214792184466</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>-36.72284798891532,175.72233904322297</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>-36.72265590969991,175.72320552659164</t>
+        </is>
+      </c>
+      <c r="J356" t="inlineStr">
+        <is>
+          <t>-36.722448759828254,175.72405200349442</t>
+        </is>
+      </c>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>-36.72213846049217,175.72483812345394</t>
+        </is>
+      </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>-36.72182562386728,175.72564692441154</t>
+        </is>
+      </c>
+      <c r="M356" t="inlineStr">
+        <is>
+          <t>-36.72141162175466,175.72637250961373</t>
+        </is>
+      </c>
+      <c r="N356" t="inlineStr">
+        <is>
+          <t>-36.720931844284635,175.72703098357144</t>
+        </is>
+      </c>
+      <c r="O356" t="inlineStr">
+        <is>
+          <t>-36.72045236503127,175.72763054595833</t>
+        </is>
+      </c>
+      <c r="P356" t="inlineStr">
+        <is>
+          <t>-36.71985645511685,175.72808008379283</t>
+        </is>
+      </c>
+      <c r="Q356" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:05:20+00:00</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>-36.723696796378746,175.71709872970376</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>-36.72364910732018,175.71799947616447</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>-36.72356814313662,175.71888390753418</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>-36.72341289877118,175.71974050470868</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>-36.72329394979587,175.72062890292239</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>-36.723067274751934,175.7214822667745</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>-36.72285916130177,175.7223434034138</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>-36.72267406144438,175.7232125314877</t>
+        </is>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>-36.72245565586393,175.72405559268913</t>
+        </is>
+      </c>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>-36.722148759354305,175.72484550678934</t>
+        </is>
+      </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>-36.7218260021386,175.72564722813888</t>
+        </is>
+      </c>
+      <c r="M357" t="inlineStr">
+        <is>
+          <t>-36.721415930666616,175.7263765628618</t>
+        </is>
+      </c>
+      <c r="N357" t="inlineStr">
+        <is>
+          <t>-36.720939759012545,175.72703979778424</t>
+        </is>
+      </c>
+      <c r="O357" t="inlineStr">
+        <is>
+          <t>-36.720454322183464,175.72763403458524</t>
+        </is>
+      </c>
+      <c r="P357" t="inlineStr">
+        <is>
+          <t>-36.71985197880083,175.7280672491941</t>
+        </is>
+      </c>
+      <c r="Q357" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0157/nzd0157.xlsx
+++ b/data/nzd0157/nzd0157.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q357"/>
+  <dimension ref="A1:Q358"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20786,6 +20786,63 @@
         </is>
       </c>
     </row>
+    <row r="358">
+      <c r="A358" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:04:54+00:00</t>
+        </is>
+      </c>
+      <c r="B358" t="n">
+        <v>390.54</v>
+      </c>
+      <c r="C358" t="n">
+        <v>383.09</v>
+      </c>
+      <c r="D358" t="n">
+        <v>380.58</v>
+      </c>
+      <c r="E358" t="n">
+        <v>380.29</v>
+      </c>
+      <c r="F358" t="n">
+        <v>369.76</v>
+      </c>
+      <c r="G358" t="n">
+        <v>370.18</v>
+      </c>
+      <c r="H358" t="n">
+        <v>370.12</v>
+      </c>
+      <c r="I358" t="n">
+        <v>369.02</v>
+      </c>
+      <c r="J358" t="n">
+        <v>372.05</v>
+      </c>
+      <c r="K358" t="n">
+        <v>370.08</v>
+      </c>
+      <c r="L358" t="n">
+        <v>365.01</v>
+      </c>
+      <c r="M358" t="n">
+        <v>368.14</v>
+      </c>
+      <c r="N358" t="n">
+        <v>372.4</v>
+      </c>
+      <c r="O358" t="n">
+        <v>379.25</v>
+      </c>
+      <c r="P358" t="n">
+        <v>370.66</v>
+      </c>
+      <c r="Q358" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -20797,7 +20854,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B373"/>
+  <dimension ref="A1:B374"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24530,6 +24587,16 @@
       </c>
       <c r="B373" t="n">
         <v>-0.59</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B374" t="n">
+        <v>-0.64</v>
       </c>
     </row>
   </sheetData>
@@ -24698,28 +24765,28 @@
         <v>0.0555</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2704469294764054</v>
+        <v>0.2720766313677508</v>
       </c>
       <c r="J2" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="K2" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2575053997478758</v>
+        <v>0.2606175082596677</v>
       </c>
       <c r="M2" t="n">
-        <v>2.571142679654841</v>
+        <v>2.57216886611112</v>
       </c>
       <c r="N2" t="n">
-        <v>11.63700447881723</v>
+        <v>11.62795742527552</v>
       </c>
       <c r="O2" t="n">
-        <v>3.411305392194786</v>
+        <v>3.409979094551097</v>
       </c>
       <c r="P2" t="n">
-        <v>380.3532454184222</v>
+        <v>380.3355946420447</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -24776,28 +24843,28 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3796966116751259</v>
+        <v>0.3835547018523361</v>
       </c>
       <c r="J3" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="K3" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2877210396803278</v>
+        <v>0.2917846897136858</v>
       </c>
       <c r="M3" t="n">
-        <v>3.54694519967774</v>
+        <v>3.555741708392964</v>
       </c>
       <c r="N3" t="n">
-        <v>19.69346205299707</v>
+        <v>19.77027944167622</v>
       </c>
       <c r="O3" t="n">
-        <v>4.437731633728776</v>
+        <v>4.446378238710268</v>
       </c>
       <c r="P3" t="n">
-        <v>365.9778848903743</v>
+        <v>365.9360991580734</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -24854,28 +24921,28 @@
         <v>0.1281</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3388932983688552</v>
+        <v>0.3413909215143846</v>
       </c>
       <c r="J4" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="K4" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2459235571048186</v>
+        <v>0.2492881106624214</v>
       </c>
       <c r="M4" t="n">
-        <v>3.342512439783084</v>
+        <v>3.344576025417965</v>
       </c>
       <c r="N4" t="n">
-        <v>19.43172409599416</v>
+        <v>19.43260570147169</v>
       </c>
       <c r="O4" t="n">
-        <v>4.408142930531422</v>
+        <v>4.408242926776119</v>
       </c>
       <c r="P4" t="n">
-        <v>367.0010996166304</v>
+        <v>366.9740486646427</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -24932,28 +24999,28 @@
         <v>0.09959999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2347122290314982</v>
+        <v>0.2383782071599551</v>
       </c>
       <c r="J5" t="n">
+        <v>357</v>
+      </c>
+      <c r="K5" t="n">
         <v>356</v>
       </c>
-      <c r="K5" t="n">
-        <v>355</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.1520947631400631</v>
+        <v>0.1560380550143488</v>
       </c>
       <c r="M5" t="n">
-        <v>3.138428941923333</v>
+        <v>3.147625553015822</v>
       </c>
       <c r="N5" t="n">
-        <v>16.77728883192028</v>
+        <v>16.8475773787985</v>
       </c>
       <c r="O5" t="n">
-        <v>4.09600889060562</v>
+        <v>4.104580049018231</v>
       </c>
       <c r="P5" t="n">
-        <v>367.4823563649284</v>
+        <v>367.4423790041806</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25010,28 +25077,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1464129417959582</v>
+        <v>0.1476914975886333</v>
       </c>
       <c r="J6" t="n">
+        <v>357</v>
+      </c>
+      <c r="K6" t="n">
         <v>356</v>
       </c>
-      <c r="K6" t="n">
-        <v>355</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.07553006252031047</v>
+        <v>0.07712654969674582</v>
       </c>
       <c r="M6" t="n">
-        <v>2.891173485780401</v>
+        <v>2.888000724369104</v>
       </c>
       <c r="N6" t="n">
-        <v>14.33339836024875</v>
+        <v>14.30741790677843</v>
       </c>
       <c r="O6" t="n">
-        <v>3.785947485141435</v>
+        <v>3.782514759624664</v>
       </c>
       <c r="P6" t="n">
-        <v>363.552599034231</v>
+        <v>363.5386564289102</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -25088,28 +25155,28 @@
         <v>0.1229</v>
       </c>
       <c r="I7" t="n">
-        <v>0.224460933569556</v>
+        <v>0.2259755961332019</v>
       </c>
       <c r="J7" t="n">
+        <v>357</v>
+      </c>
+      <c r="K7" t="n">
         <v>356</v>
       </c>
-      <c r="K7" t="n">
-        <v>355</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.1758496022852807</v>
+        <v>0.178495268719702</v>
       </c>
       <c r="M7" t="n">
-        <v>2.858579419682135</v>
+        <v>2.856172086368829</v>
       </c>
       <c r="N7" t="n">
-        <v>12.89923338974516</v>
+        <v>12.88304331363298</v>
       </c>
       <c r="O7" t="n">
-        <v>3.591550276655634</v>
+        <v>3.589295657038158</v>
       </c>
       <c r="P7" t="n">
-        <v>361.4565100229854</v>
+        <v>361.4399926817476</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -25166,28 +25233,28 @@
         <v>0.074</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2359776536329415</v>
+        <v>0.2383390609678114</v>
       </c>
       <c r="J8" t="n">
+        <v>357</v>
+      </c>
+      <c r="K8" t="n">
         <v>356</v>
       </c>
-      <c r="K8" t="n">
-        <v>355</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.1503437591635388</v>
+        <v>0.1533484846496634</v>
       </c>
       <c r="M8" t="n">
-        <v>3.251036327251109</v>
+        <v>3.2523369063811</v>
       </c>
       <c r="N8" t="n">
-        <v>17.19162354171575</v>
+        <v>17.19205035542765</v>
       </c>
       <c r="O8" t="n">
-        <v>4.14627827596216</v>
+        <v>4.146329745139386</v>
       </c>
       <c r="P8" t="n">
-        <v>359.5937929213716</v>
+        <v>359.5680418586018</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -25244,28 +25311,28 @@
         <v>0.09089999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2305644049978862</v>
+        <v>0.2313810634794064</v>
       </c>
       <c r="J9" t="n">
+        <v>357</v>
+      </c>
+      <c r="K9" t="n">
         <v>356</v>
       </c>
-      <c r="K9" t="n">
-        <v>355</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.155799946177791</v>
+        <v>0.1575114655711848</v>
       </c>
       <c r="M9" t="n">
-        <v>3.16174421397743</v>
+        <v>3.157013676746187</v>
       </c>
       <c r="N9" t="n">
-        <v>15.7354759195712</v>
+        <v>15.69710191106119</v>
       </c>
       <c r="O9" t="n">
-        <v>3.96679668240902</v>
+        <v>3.961956828520623</v>
       </c>
       <c r="P9" t="n">
-        <v>361.3689359066347</v>
+        <v>361.360030275019</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -25322,28 +25389,28 @@
         <v>0.0915</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1578844368100256</v>
+        <v>0.1580096125132936</v>
       </c>
       <c r="J10" t="n">
+        <v>357</v>
+      </c>
+      <c r="K10" t="n">
         <v>356</v>
       </c>
-      <c r="K10" t="n">
-        <v>355</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.08519987588368816</v>
+        <v>0.08581216526517621</v>
       </c>
       <c r="M10" t="n">
-        <v>2.985146126467936</v>
+        <v>2.977465102176371</v>
       </c>
       <c r="N10" t="n">
-        <v>14.62120566604209</v>
+        <v>14.58027175834406</v>
       </c>
       <c r="O10" t="n">
-        <v>3.823768516273192</v>
+        <v>3.818412203828191</v>
       </c>
       <c r="P10" t="n">
-        <v>367.5773903288945</v>
+        <v>367.5760252923145</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -25400,28 +25467,28 @@
         <v>0.0954</v>
       </c>
       <c r="I11" t="n">
-        <v>0.159859723582522</v>
+        <v>0.1608870734835558</v>
       </c>
       <c r="J11" t="n">
+        <v>357</v>
+      </c>
+      <c r="K11" t="n">
         <v>356</v>
       </c>
-      <c r="K11" t="n">
-        <v>355</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.08234667367901205</v>
+        <v>0.08375337360843604</v>
       </c>
       <c r="M11" t="n">
-        <v>3.15372458020981</v>
+        <v>3.149995105932081</v>
       </c>
       <c r="N11" t="n">
-        <v>15.557076467002</v>
+        <v>15.5225979288532</v>
       </c>
       <c r="O11" t="n">
-        <v>3.944245994737397</v>
+        <v>3.939872831558552</v>
       </c>
       <c r="P11" t="n">
-        <v>363.9645352032405</v>
+        <v>363.953331989209</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -25478,28 +25545,28 @@
         <v>0.0953</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1714620715986921</v>
+        <v>0.1705514592481923</v>
       </c>
       <c r="J12" t="n">
+        <v>357</v>
+      </c>
+      <c r="K12" t="n">
         <v>356</v>
       </c>
-      <c r="K12" t="n">
-        <v>355</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.09139670222770657</v>
+        <v>0.09099471740881193</v>
       </c>
       <c r="M12" t="n">
-        <v>3.135151171979742</v>
+        <v>3.130126409764764</v>
       </c>
       <c r="N12" t="n">
-        <v>15.96603969882251</v>
+        <v>15.92843586144805</v>
       </c>
       <c r="O12" t="n">
-        <v>3.995752707416028</v>
+        <v>3.99104445746324</v>
       </c>
       <c r="P12" t="n">
-        <v>362.0114923888731</v>
+        <v>362.0214225840793</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -25556,28 +25623,28 @@
         <v>0.0854</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2593712127634435</v>
+        <v>0.257716005533028</v>
       </c>
       <c r="J13" t="n">
+        <v>357</v>
+      </c>
+      <c r="K13" t="n">
         <v>356</v>
       </c>
-      <c r="K13" t="n">
-        <v>355</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.1552895880160808</v>
+        <v>0.1542757702178418</v>
       </c>
       <c r="M13" t="n">
-        <v>3.385199953313743</v>
+        <v>3.384102581171649</v>
       </c>
       <c r="N13" t="n">
-        <v>19.99062368192909</v>
+        <v>19.9584062356747</v>
       </c>
       <c r="O13" t="n">
-        <v>4.471087527876086</v>
+        <v>4.467483210452468</v>
       </c>
       <c r="P13" t="n">
-        <v>364.099017840108</v>
+        <v>364.1170678159245</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -25634,28 +25701,28 @@
         <v>0.0863</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3046956723872619</v>
+        <v>0.3032411436370522</v>
       </c>
       <c r="J14" t="n">
+        <v>357</v>
+      </c>
+      <c r="K14" t="n">
         <v>356</v>
       </c>
-      <c r="K14" t="n">
-        <v>355</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.1599189019317211</v>
+        <v>0.1593807700227899</v>
       </c>
       <c r="M14" t="n">
-        <v>3.978646862581065</v>
+        <v>3.973876631022874</v>
       </c>
       <c r="N14" t="n">
-        <v>26.64227303493353</v>
+        <v>26.58591899032946</v>
       </c>
       <c r="O14" t="n">
-        <v>5.161615351315277</v>
+        <v>5.15615350725029</v>
       </c>
       <c r="P14" t="n">
-        <v>366.7858470949799</v>
+        <v>366.8017086791268</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -25712,28 +25779,28 @@
         <v>0.0477</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5288816669204726</v>
+        <v>0.5260035784249726</v>
       </c>
       <c r="J15" t="n">
+        <v>357</v>
+      </c>
+      <c r="K15" t="n">
         <v>356</v>
       </c>
-      <c r="K15" t="n">
-        <v>355</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.1931868166892452</v>
+        <v>0.1922851375392262</v>
       </c>
       <c r="M15" t="n">
-        <v>5.796282493817581</v>
+        <v>5.793404182581019</v>
       </c>
       <c r="N15" t="n">
-        <v>63.81603457455267</v>
+        <v>63.7091454470192</v>
       </c>
       <c r="O15" t="n">
-        <v>7.988493886494042</v>
+        <v>7.981800889963317</v>
       </c>
       <c r="P15" t="n">
-        <v>370.1222696050282</v>
+        <v>370.1536550574277</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -25790,28 +25857,28 @@
         <v>0.0274</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.01563928132118662</v>
+        <v>-0.01351474337837109</v>
       </c>
       <c r="J16" t="n">
+        <v>357</v>
+      </c>
+      <c r="K16" t="n">
         <v>356</v>
       </c>
-      <c r="K16" t="n">
-        <v>355</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.000150905525866607</v>
+        <v>0.0001133511429076695</v>
       </c>
       <c r="M16" t="n">
-        <v>6.710152652863343</v>
+        <v>6.703732326194426</v>
       </c>
       <c r="N16" t="n">
-        <v>88.52790503451905</v>
+        <v>88.31866558123293</v>
       </c>
       <c r="O16" t="n">
-        <v>9.408926880070812</v>
+        <v>9.397801103515276</v>
       </c>
       <c r="P16" t="n">
-        <v>367.3167982988438</v>
+        <v>367.2936302883468</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -25849,7 +25916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q357"/>
+  <dimension ref="A1:Q358"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56863,6 +56930,93 @@
         </is>
       </c>
     </row>
+    <row r="358">
+      <c r="A358" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:04:54+00:00</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>-36.72368906825191,175.71709711085722</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>-36.72364884083344,175.7179994203402</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>-36.72356655640938,175.71888349265453</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>-36.72341039171312,175.7197395924243</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>-36.72328805322387,175.720626460536</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>-36.72306941620772,175.72148313277688</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>-36.722864575612064,175.72234551642984</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>-36.722673373226584,175.72321226589915</t>
+        </is>
+      </c>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>-36.72245141854082,175.72405338728024</t>
+        </is>
+      </c>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>-36.722147823094126,175.72484483557696</t>
+        </is>
+      </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>-36.72182229507958,175.72564425161087</t>
+        </is>
+      </c>
+      <c r="M358" t="inlineStr">
+        <is>
+          <t>-36.72141205264587,175.7263729149385</t>
+        </is>
+      </c>
+      <c r="N358" t="inlineStr">
+        <is>
+          <t>-36.720933789429694,175.72703314977613</t>
+        </is>
+      </c>
+      <c r="O358" t="inlineStr">
+        <is>
+          <t>-36.72043959203531,175.72760777808185</t>
+        </is>
+      </c>
+      <c r="P358" t="inlineStr">
+        <is>
+          <t>-36.71984635654587,175.72805112894014</t>
+        </is>
+      </c>
+      <c r="Q358" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
